--- a/medford_endoskopy_dlya_otorinolaringologii.xlsx
+++ b/medford_endoskopy_dlya_otorinolaringologii.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопы для оториноларингологии для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Pentax, ATMOS — всего 7 позиций.</t>
+          <t>Эндоскопы для оториноларингологии для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Pentax, ATMOS.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_endoskopy_dlya_otorinolaringologii.xlsx
+++ b/medford_endoskopy_dlya_otorinolaringologii.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать эндоскопы для оториноларингологии для клиники?</t>
+          <t>Что ЛОР смотрит эндоскопом?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Рабочая длина, мм, Угол поля зрения, °, Глубина резкости, мм, Диаметр вводимой трубки, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>ЛОР-эндоскопом осматривают полость носа, околоносовые пазухи, носоглотку, гортань, а видеоотоскопом — наружный слуховой проход и барабанную перепонку. Прибор даёт увеличенное изображение слизистой и структур, недоступных обычному осмотру. Что именно исследовать и каким прибором, определяет врач по клинической ситуации.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем отличается жёсткий ЛОР-эндоскоп от гибкого?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Жёсткий эндоскоп имеет стандартные диаметры 2,7 и 4 мм и даёт прямой доступ к полости носа и пазухам. Гибкий назофаринголарингоскоп (диаметр в линейке 3,0–4,8 мм) проходит по естественному изгибу и позволяет осмотреть носоглотку и гортань с меньшим дискомфортом. Выбор зависит от зоны осмотра.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Чем ларингоскопия отличается от эндоскопии?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Olympus, Pentax, ATMOS. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Ларингоскопия — это осмотр гортани, частный случай эндоскопического исследования ЛОР-органов. Эндоскопия ЛОР-органов шире и включает осмотр носа, носоглотки, пазух и уха. Для осмотра гортани применяют, в частности, гибкие ларингофиброскопы. Показания и метод определяет врач.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Можно ли делать эндоскопию детям?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Возможность и целесообразность эндоскопического осмотра у ребёнка определяет врач с учётом показаний, возраста и диаметра прибора. Для детей обычно предпочтительны более тонкие гибкие эндоскопы, которые переносятся легче. Решение о процедуре принимается индивидуально, самостоятельно назначать её не следует.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Что такое chip-on-the-tip?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Chip-on-the-tip — схема, при которой видеоматрица расположена на дистальном конце эндоскопа, как у видеоназофарингоскопа Otopront. Изображение формируется прямо на кончике прибора и передаётся на монитор без волоконного жгута. Это повышает качество картинки и удобно для документирования исследования.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что лор смотрит эндоскопом?</t>
+          <t>Нужен ли отдельный источник света?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Да, эндоскопическое исследование требует источника света, а для видеосистемы — камеры и монитора. Эндоскоп, источник света и камера должны быть совместимы по разъёмам и протоколу. Если оборудования ещё нет, комплект планируют целиком; совместимость моделей сверяют до заказа.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит эндоскопия носа?</t>
+          <t>Нужна ли регистрация Росздравнадзора?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Для применения в клинике ЛОР-эндоскоп должен быть зарегистрированным медицинским изделием с действующим регистрационным удостоверением Росздравнадзора. Статус регистрации уточняют до покупки — это условие законной эксплуатации. Технические и бытовые эндоскопы к медицинскому применению не допускаются.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Как продлить срок службы гибкого эндоскопа?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Ресурс гибкого ЛОР-эндоскопа зависит от аккуратной эксплуатации и корректной дезинфекции по инструкции производителя. Наиболее уязвимы изгибаемая часть и вводимая трубка. Правильное хранение, бережное обращение при манипуляциях и плановое обслуживание снижают риск повреждений и продлевают срок службы прибора.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>endoskopy_dlya_otorinolaringologii</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопы для оториноларингологии для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Olympus, Pentax, ATMOS.</t>
+          <t>Эндоскопы для оториноларингологии — приборы для осмотра уха, горла и носа. В категории представлены гибкие назофаринголарингоскопы, риноларингофиброскопы, видеоотоскоп и источник света брендов Olympus, Pentax, ATMOS, Otopront и ОПТИMED. Диаметр дистального конца моделей — от 3,0 мм у Pentax VNL9-CP до 4,8 мм у Olympus ENF-T3, рабочая длина — 300–600 мм. Видеоназофарингоскоп Otopront построен по схеме chip-on-the-tip с матрицей на дистальном конце, видеоотоскоп ОПТИMED В0-01 имеет поле зрения 55°.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Жёсткие и гибкие ЛОР-эндоскопы</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое эндоскопы для оториноларингологии</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3477,243 +3515,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Жёсткие и гибкие ЛОР-эндоскопы</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Признак</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Жёсткий эндоскоп</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Рабочая длина, мм</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Угол поля зрения, °</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Глубина резкости, мм</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Диаметр вводимой трубки, мм</t>
+          <t>Гибкий эндоскоп</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Видеоназофарингоскоп Otopront Chip-on-the-Tip</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Диаметр</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>стандартно 2,7 и 4 мм</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>12,0</t>
+          <t>3,0–4,8 мм (в линейке)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Ларингофиброскоп интубационный Olympus LF-GP</t>
+          <t>Зона осмотра</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Olympus</t>
+          <t>полость носа, околоносовые пазухи</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>90°</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>4-50</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>4,1</t>
+          <t>носоглотка, гортань</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Pentax VNL9-CP видеоназофаринголарингоскоп</t>
+          <t>Комфорт пациента</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Pentax</t>
+          <t>требует прямого доступа</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>90°</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>5-50</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>проходит по естественному изгибу</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Гибкий видео-назофарингоскоп ATMOS Scope</t>
+          <t>Примеры в категории</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ATMOS</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>80°</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>6 мм - бесконечность</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Риноларингофиброскоп Olympus ENF-T3</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Olympus</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>85º</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>3-50</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Видеоотоскоп ОПТИMED В0-01</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Pentax VNL9-CP, Olympus ENF-T3, ATMOS Scope</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3725,7 +3629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4051,12 +3955,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите зону осмотра</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается эндоскопы для оториноларингологии: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала фиксируют, что нужно осматривать: полость носа и околоносовые пазухи, носоглотку и гортань или наружный слуховой проход и барабанную перепонку. Для гортани и носоглотки берут гибкий назофаринголарингоскоп, для уха — видеоотоскоп. Зона осмотра определяет тип прибора раньше, чем бренд и цена.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -4096,12 +4000,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Выберите жёсткий или гибкий тип</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Жёсткие ЛОР-эндоскопы стандартных диаметров 2,7 и 4 мм дают прямой доступ к полости носа и пазухам. Гибкие проходят по естественному изгибу и осматривают гортань с меньшим дискомфортом. Выбор зависит от процедур кабинета и переносимости пациентами, включая детей, что оценивает врач.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -4141,12 +4045,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Сверьте диаметр и рабочую длину</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Рабочая длина, мм, Угол поля зрения, °, Глубина резкости, мм, Диаметр вводимой трубки, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Диаметр дистального конца определяет проходимость и комфорт: в линейке это 3,0–4,8 мм. Рабочая длина должна доставать до целевой зоны — у ЛОР-моделей обычно 300–600 мм. Тонкие приборы, например Pentax VNL9-CP (3,0 мм), переносятся легче; выбор диаметра согласуют с пациентской группой.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -4186,12 +4090,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените тип визуализации</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Olympus, Pentax, ATMOS.</t>
+          <t>Различают фиброскопы с волоконной оптикой и видеоэндоскопы с матрицей на дистальном конце (chip-on-the-tip, как у Otopront). Видеосхема даёт изображение прямо с кончика прибора и удобна для вывода на монитор и документирования. Тип визуализации выбирают под задачи кабинета и наличие видеостойки.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -4231,12 +4135,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте совместимость с источником света и камерой</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Эндоскоп работает в паре с источником света и, для видеосистемы, с камерой и монитором. Разъёмы и протокол должны совпадать. Если стойки ещё нет, планируют комплект целиком, включая источник света. Совместимость сверяют по моделям до заказа, иначе оборудование не даст качественного изображения.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -4276,12 +4180,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните регистрацию и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Для клинического применения ЛОР-эндоскоп должен быть зарегистрированным медицинским изделием с действующим РУ Росздравнадзора. Заранее уточняют условия гарантии, доступность запчастей и сервис. Для гибких приборов важна корректная дезинфекция по инструкции — это продлевает ресурс изгибаемой части и канала.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -4331,7 +4235,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопы для оториноларингологии подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Olympus, Pentax, ATMOS. При выборе обращают внимание на рабочая длина, угол поля зрения, глубина резкости, диаметр вводимой трубки, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>ЛОР-эндоскоп подбирают по зоне осмотра и переносимости пациентом. Гибкий назофаринголарингоскоп удобен для гортани и носоглотки, потому что проходит по естественному изгибу; жёсткий инструмент даёт прямой доступ к полости носа и пазухам. Для видеосистемы важна совместимость эндоскопа с источником света и камерой: без согласованной пары изображение теряет в качестве. Схема chip-on-the-tip даёт картинку прямо с дистального конца.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -4615,13 +4519,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое эндоскопы для оториноларингологии</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопы для оториноларингологии — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Olympus, Pentax, ATMOS. Подберём вариант под задачи вашего отделения.</t>
+          <t>ЛОР-эндоскоп — прибор для осмотра полости носа, носоглотки, гортани и слухового прохода. Различают жёсткие эндоскопы стандартных диаметров 2,7 и 4 мм для полости носа и пазух и гибкие назофаринголарингоскопы, которые проходят по естественному изгибу и позволяют осмотреть гортань с меньшим дискомфортом. Тип выбирают по зоне осмотра и задачам кабинета; ключевые параметры — диаметр дистального конца (в линейке 3,0–4,8 мм), рабочая длина и угол поля зрения. Необходимость осмотра и его вид определяет врач.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4658,13 +4562,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>ЛОР-эндоскопы: назначение</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Рабочая длина, мм, Угол поля зрения, °, Глубина резкости, мм, Диаметр вводимой трубки, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Эндоскопы для оториноларингологии применяют для осмотра уха, горла и носа: полости носа, околоносовых пазух, носоглотки, гортани и наружного слухового прохода. Прибор даёт увеличенное изображение слизистой и структур, недоступных при обычном осмотре, и позволяет выводить картинку на монитор для документирования. Вид исследования и показания определяет врач.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4701,13 +4605,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Жёсткие и гибкие ЛОР-эндоскопы</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Жёсткие ЛОР-эндоскопы стандартных диаметров 2,7 и 4 мм дают прямой доступ к полости носа и пазухам. Гибкие назофаринголарингоскопы проходят по естественному изгибу и удобны для осмотра носоглотки и гортани с меньшим дискомфортом. В категории представлены гибкие модели Olympus, Pentax и ATMOS с диаметром дистального конца 3,0–4,8 мм.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4744,13 +4648,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Характеристики при выборе</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>При подборе ЛОР-эндоскопа сравнивают диаметр дистального конца и вводимой трубки, рабочую длину (в линейке 300–600 мм), угол поля зрения и глубину резкости, а также тип визуализации — фиброоптика или видеоматрица chip-on-the-tip. Отдельно проверяют совместимость с источником света, камерой и монитором и наличие регистрационного удостоверения.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4767,6 +4671,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Бренды и видеосистема</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>В категории представлены эндоскопы Olympus, Pentax, ATMOS, Otopront, видеоотоскоп ОПТИMED и источник света Euroclinic. Для полноценной видеосистемы эндоскоп дополняют совместимым источником света и камерой с выводом на монитор. Комплект планируют с учётом уже имеющегося оборудования, сверяя разъёмы и протокол передачи изображения до заказа.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>endoskopy_dlya_otorinolaringologii</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
